--- a/results/07-2026/beta/contributions-07-2026.xlsx
+++ b/results/07-2026/beta/contributions-07-2026.xlsx
@@ -2786,16 +2786,16 @@
         <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.172652474863118</v>
+        <v>-0.0273475251368821</v>
       </c>
       <c r="AD23" t="n">
         <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.2331894038576</v>
+        <v>-0.4331894038576</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.046173352173961</v>
+        <v>-0.00382664782603898</v>
       </c>
     </row>
     <row r="24">
@@ -2893,7 +2893,7 @@
         <v>0.26031492736318</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.039150923320437</v>
+        <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
@@ -2991,7 +2991,7 @@
         <v>-1.22424133666683</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.473042371556266</v>
+        <v>-0.523042371556266</v>
       </c>
     </row>
     <row r="26">
@@ -3080,16 +3080,16 @@
         <v>-0.0696095758028083</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.386162553483636</v>
+        <v>0.446162553483636</v>
       </c>
       <c r="AD26" t="n">
         <v>0.143565841710704</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.758904077301381</v>
+        <v>0.818904077301381</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.109552933964968</v>
+        <v>-0.144552933964968</v>
       </c>
     </row>
     <row r="27">
@@ -3178,16 +3178,16 @@
         <v>-0.393041613759915</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.274423756613508</v>
+        <v>0.334423756613508</v>
       </c>
       <c r="AD27" t="n">
         <v>0.417671871417178</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.218459489374329</v>
+        <v>-0.158459489374329</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.10587045534415</v>
+        <v>-0.0758704553441498</v>
       </c>
     </row>
     <row r="28">
@@ -3276,16 +3276,16 @@
         <v>-0.0388741365488032</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.00270540138671922</v>
+        <v>0.0627054013867192</v>
       </c>
       <c r="AD28" t="n">
         <v>-0.0357858960579702</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.480129880866155</v>
+        <v>-0.420129880866155</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.290981657401484</v>
+        <v>-0.245981657401484</v>
       </c>
     </row>
     <row r="29">
@@ -3374,16 +3374,16 @@
         <v>-0.00921784082785182</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.222168421360049</v>
+        <v>-0.162168421360049</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.161029071650163</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.53110091196003</v>
+        <v>-0.47110091196003</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.117696551224783</v>
+        <v>-0.0576965512247833</v>
       </c>
     </row>
     <row r="30">
@@ -3472,16 +3472,16 @@
         <v>0.062322220140975</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.525330027874355</v>
+        <v>-0.465330027874355</v>
       </c>
       <c r="AD30" t="n">
         <v>-0.323163577136945</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.827244906389214</v>
+        <v>-0.767244906389214</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.514233797147432</v>
+        <v>-0.454233797147432</v>
       </c>
     </row>
     <row r="31">
@@ -3570,16 +3570,16 @@
         <v>-0.0452037874837307</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.583530017202277</v>
+        <v>-0.523530017202277</v>
       </c>
       <c r="AD31" t="n">
         <v>-0.176968014107152</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.863692124588244</v>
+        <v>-0.803692124588244</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.675541955950911</v>
+        <v>-0.615541955950911</v>
       </c>
     </row>
     <row r="32">
@@ -3677,7 +3677,7 @@
         <v>-0.690644749508038</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.728170673111381</v>
+        <v>-0.683170673111381</v>
       </c>
     </row>
     <row r="33">
@@ -3775,7 +3775,7 @@
         <v>-0.689793416877435</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.767843799340733</v>
+        <v>-0.737843799340733</v>
       </c>
     </row>
     <row r="34">
@@ -3873,7 +3873,7 @@
         <v>-0.783675786582959</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.756951519389169</v>
+        <v>-0.741951519389169</v>
       </c>
     </row>
     <row r="35">
